--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线3层（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="483">
   <si>
     <t>ID</t>
   </si>
@@ -186,9 +186,18 @@
     <t>12</t>
   </si>
   <si>
+    <t>克拉克</t>
+  </si>
+  <si>
+    <t>Clark_default</t>
+  </si>
+  <si>
     <t>怎么了？</t>
   </si>
   <si>
+    <t>charfadein(L,1)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=11</t>
   </si>
   <si>
@@ -196,6 +205,9 @@
   </si>
   <si>
     <t>没等你进一步在这片黑暗中锁定声音的来源，耳边便传来了同伴的轻声关切。醇厚温和的男音在这片冰冷的空气中蒸开一片热雾，越发衬得那声呼唤像某种空穴来风的幻听。</t>
+  </si>
+  <si>
+    <t>charfadeout(L,1)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=12</t>
@@ -300,18 +312,9 @@
     <t>21</t>
   </si>
   <si>
-    <t>克拉克</t>
-  </si>
-  <si>
-    <t>Clark_default</t>
-  </si>
-  <si>
     <t>什么声音？刚才走得有些急，可能是被脚步声盖过去了吧。</t>
   </si>
   <si>
-    <t>charfadein(L,1)</t>
-  </si>
-  <si>
     <t>源类型=type:txt_Clark; 层级=19</t>
   </si>
   <si>
@@ -319,9 +322,6 @@
   </si>
   <si>
     <t>他并没有对你的听觉提出怀疑，而是第一时间将感知的差异归因于自己的漏判。这过于正常的反应，反倒让你更加确信了它的确发生过——因为那声音分明不是从外面，而是直接在你脑海内部响起。</t>
-  </si>
-  <si>
-    <t>charfadeout(L,1)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=20</t>
@@ -836,6 +836,9 @@
     <t>克拉克猛地退后几步，手中的电筒险些因为惊吓而抖落到地上。你赶紧跟过去，配枪的准心往门口一送，确认危险不是来自门外的其他东西后这才将注意力转回了那面镜子。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=68</t>
   </si>
   <si>
@@ -852,6 +855,9 @@
   </si>
   <si>
     <t>只见两个渗人的面孔赫然倒映于那片被手指反复擦拭过的区域——</t>
+  </si>
+  <si>
+    <t>10 enhanced suspense</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=70</t>
@@ -953,7 +959,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>bgfade(sntzm_clark3F(2)_90,1)&amp;loadScript(</t>
+      <t>parallel(charfadeout(L,1);bgfade(sntzm_clark3F(2)_90,1))&amp;loadScript(</t>
     </r>
     <r>
       <rPr>
@@ -1142,6 +1148,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -3369,13 +3380,13 @@
         <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3384,7 +3395,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3396,15 +3407,15 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="L13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="54" spans="1:12">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3413,7 +3424,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3422,7 +3433,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3434,15 +3445,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="L14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3460,7 +3471,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3475,12 +3486,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="30" spans="1:12">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3510,15 +3521,15 @@
         <v>15</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3551,12 +3562,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" ht="67.5" spans="1:12">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3574,7 +3585,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3586,18 +3597,18 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -3612,7 +3623,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3627,12 +3638,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" ht="27" spans="1:12">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3650,7 +3661,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3665,21 +3676,21 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" ht="27" spans="1:12">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3688,7 +3699,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3700,15 +3711,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="L21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" ht="55.5" spans="1:12">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3717,7 +3728,7 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3726,7 +3737,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3738,7 +3749,7 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="L22" t="s">
         <v>83</v>
@@ -4167,13 +4178,13 @@
         <v>116</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4194,7 +4205,7 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="L34" t="s">
         <v>118</v>
@@ -4211,7 +4222,7 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4232,7 +4243,7 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="L35" t="s">
         <v>121</v>
@@ -4661,13 +4672,13 @@
         <v>156</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4688,7 +4699,7 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="L47" t="s">
         <v>158</v>
@@ -4699,13 +4710,13 @@
         <v>159</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4743,7 +4754,7 @@
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4764,7 +4775,7 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="L49" t="s">
         <v>164</v>
@@ -4775,7 +4786,7 @@
         <v>165</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -4813,13 +4824,13 @@
         <v>168</v>
       </c>
       <c r="B51" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4840,7 +4851,7 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="L51" t="s">
         <v>170</v>
@@ -4857,7 +4868,7 @@
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4878,7 +4889,7 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="L52" t="s">
         <v>173</v>
@@ -4889,7 +4900,7 @@
         <v>174</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4927,13 +4938,13 @@
         <v>177</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4954,7 +4965,7 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="L54" t="s">
         <v>179</v>
@@ -5003,7 +5014,7 @@
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5035,13 +5046,13 @@
         <v>186</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5070,13 +5081,13 @@
         <v>189</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5114,7 +5125,7 @@
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5135,7 +5146,7 @@
         <v>15</v>
       </c>
       <c r="K59" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="L59" t="s">
         <v>194</v>
@@ -5146,7 +5157,7 @@
         <v>195</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -5222,13 +5233,13 @@
         <v>201</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5249,7 +5260,7 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="L62" t="s">
         <v>203</v>
@@ -5266,7 +5277,7 @@
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5287,7 +5298,7 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="L63" t="s">
         <v>206</v>
@@ -5298,7 +5309,7 @@
         <v>207</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -5599,7 +5610,7 @@
         <v>232</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
@@ -5658,7 +5669,7 @@
         <v>15</v>
       </c>
       <c r="I73" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="J73" t="s">
         <v>15</v>
@@ -5667,12 +5678,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5690,7 +5701,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5705,12 +5716,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="75" ht="28.5" spans="1:12">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="75" ht="30" spans="1:12">
       <c r="A75" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5728,13 +5739,13 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
       </c>
       <c r="I75" t="s">
-        <v>15</v>
+        <v>245</v>
       </c>
       <c r="J75" t="s">
         <v>15</v>
@@ -5743,12 +5754,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" ht="67.5" spans="1:12">
       <c r="A76" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5766,7 +5777,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5778,15 +5789,15 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L76" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77" ht="54" spans="1:12">
       <c r="A77" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5804,7 +5815,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5819,21 +5830,21 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78" ht="27" spans="1:12">
       <c r="A78" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -5842,7 +5853,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5854,15 +5865,15 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="L78" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79" ht="67.5" spans="1:12">
       <c r="A79" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5871,7 +5882,7 @@
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -5880,7 +5891,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5892,15 +5903,15 @@
         <v>15</v>
       </c>
       <c r="K79" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="L79" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="80" ht="67.5" spans="1:12">
       <c r="A80" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5918,7 +5929,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5933,12 +5944,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81" ht="67.5" spans="1:12">
       <c r="A81" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5956,7 +5967,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5971,15 +5982,15 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B82" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -5994,7 +6005,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -6009,12 +6020,12 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83" ht="27" spans="1:12">
       <c r="A83" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -6032,7 +6043,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -6047,21 +6058,21 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="84" ht="28.5" spans="1:12">
       <c r="A84" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -6070,7 +6081,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6081,13 +6092,16 @@
       <c r="J84" t="s">
         <v>15</v>
       </c>
+      <c r="K84" t="s">
+        <v>53</v>
+      </c>
       <c r="L84" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="85" ht="40.5" spans="1:12">
       <c r="A85" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6096,7 +6110,7 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E85" t="s">
         <v>15</v>
@@ -6105,7 +6119,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6117,15 +6131,15 @@
         <v>15</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L85" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="86" ht="90" spans="1:12">
       <c r="A86" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6143,7 +6157,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6155,12 +6169,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="87" ht="30" spans="1:12">
       <c r="A87" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6178,7 +6192,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6193,12 +6207,12 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="88" ht="40.5" spans="1:12">
       <c r="A88" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6216,7 +6230,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6228,15 +6242,15 @@
         <v>15</v>
       </c>
       <c r="K88" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L88" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6263,15 +6277,15 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" ht="30" spans="1:12">
       <c r="A90" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B90" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -6286,7 +6300,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6301,12 +6315,12 @@
         <v>137</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="91" ht="57" spans="1:12">
       <c r="A91" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6324,7 +6338,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6339,12 +6353,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="92" ht="40.5" spans="1:12">
       <c r="A92" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6362,7 +6376,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6377,12 +6391,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" ht="27" spans="1:12">
       <c r="A93" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6400,7 +6414,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6415,12 +6429,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94" ht="40.5" spans="1:12">
       <c r="A94" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6438,7 +6452,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6458,7 +6472,7 @@
     </row>
     <row r="95" ht="54" spans="1:12">
       <c r="A95" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6476,7 +6490,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6488,10 +6502,10 @@
         <v>15</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L95" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -6512,39 +6526,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6552,7 +6566,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -6560,7 +6574,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6568,7 +6582,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
@@ -6576,58 +6590,58 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -6649,616 +6663,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F5" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D7" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F8" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C10" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C11" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B12" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E12" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F12" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C13" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D13" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E13" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F15" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B16" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C16" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D16" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E16" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F16" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C17" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D17" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E17" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F17" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B18" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C18" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D18" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E18" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F18" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B19" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C19" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D19" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E19" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F19" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B20" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C20" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D20" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E20" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F20" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B21" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C21" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D21" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E21" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F21" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B22" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C22" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D22" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E22" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F22" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B23" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C23" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D23" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E23" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F23" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B24" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C24" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D24" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E24" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F24" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B25" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C25" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D25" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E25" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F25" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B26" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C26" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D26" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E26" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F26" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B27" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C27" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D27" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E27" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F27" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B28" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C28" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D28" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E28" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F28" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B29" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C29" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D29" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E29" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F29" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B30" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C30" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D30" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E30" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F30" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D31" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线3层（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="482">
   <si>
     <t>ID</t>
   </si>
@@ -539,18 +539,12 @@
     <t>源类型=type:txt_pb; 层级=35</t>
   </si>
   <si>
-    <t>41</t>
+    <t>42</t>
   </si>
   <si>
     <t>散落一地的实验记录纸像是被人洗劫过似得，如雪花般洒得纷纷扬扬。你捡起几张实验材料放在电筒下阅读，除开大片看不懂的参数和复杂的专业术语外，一个名词死死攥住了你的眼球——造梦设备。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=36</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
     <t>bgfade(sntzm_clark3F(2)_42,1)</t>
   </si>
   <si>
@@ -858,6 +852,9 @@
   </si>
   <si>
     <t>10 enhanced suspense</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music10)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=70</t>
@@ -2906,7 +2903,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4471,15 +4468,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="L41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="42" ht="55.5" spans="1:12">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" ht="40.5" spans="1:12">
       <c r="A42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4497,7 +4494,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4509,15 +4506,15 @@
         <v>15</v>
       </c>
       <c r="K42" t="s">
-        <v>143</v>
+        <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="43" ht="40.5" spans="1:12">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4535,7 +4532,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>146</v>
+        <v>15</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4553,7 +4550,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" ht="90" spans="1:12">
       <c r="A44" t="s">
         <v>148</v>
       </c>
@@ -4573,7 +4570,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>149</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4585,15 +4582,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="L44" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" ht="90" spans="1:12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4611,7 +4608,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4623,24 +4620,24 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="46" ht="40.5" spans="1:12">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4649,7 +4646,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4661,15 +4658,15 @@
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="L46" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" ht="54" spans="1:12">
       <c r="A47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
@@ -4687,7 +4684,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4699,18 +4696,18 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="48" ht="54" spans="1:12">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -4725,7 +4722,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4737,24 +4734,24 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="L48" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="49" ht="40.5" spans="1:12">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" ht="27" spans="1:12">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4763,7 +4760,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4775,24 +4772,24 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" ht="27" spans="1:12">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4801,7 +4798,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4813,18 +4810,18 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="L50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" ht="27" spans="1:12">
       <c r="A51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -4839,7 +4836,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4851,24 +4848,24 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L51" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="52" ht="27" spans="1:12">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4877,7 +4874,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4889,24 +4886,24 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4915,7 +4912,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4927,25 +4924,22 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="L53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
-      <c r="D54" t="s">
-        <v>51</v>
-      </c>
       <c r="E54" t="s">
         <v>15</v>
       </c>
@@ -4953,7 +4947,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>178</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4963,15 +4957,12 @@
       </c>
       <c r="J54" t="s">
         <v>15</v>
-      </c>
-      <c r="K54" t="s">
-        <v>53</v>
       </c>
       <c r="L54" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" ht="150" spans="1:12">
       <c r="A55" t="s">
         <v>180</v>
       </c>
@@ -4981,6 +4972,9 @@
       <c r="C55" t="s">
         <v>14</v>
       </c>
+      <c r="D55" t="s">
+        <v>51</v>
+      </c>
       <c r="E55" t="s">
         <v>15</v>
       </c>
@@ -4988,7 +4982,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>15</v>
+        <v>181</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4999,16 +4993,19 @@
       <c r="J55" t="s">
         <v>15</v>
       </c>
+      <c r="K55" t="s">
+        <v>182</v>
+      </c>
       <c r="L55" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="56" ht="150" spans="1:12">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" ht="27" spans="1:12">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -5023,7 +5020,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -5034,16 +5031,13 @@
       <c r="J56" t="s">
         <v>15</v>
       </c>
-      <c r="K56" t="s">
-        <v>184</v>
-      </c>
       <c r="L56" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="57" ht="27" spans="1:12">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="57" ht="42" spans="1:12">
       <c r="A57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s">
         <v>50</v>
@@ -5061,7 +5055,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -5072,16 +5066,19 @@
       <c r="J57" t="s">
         <v>15</v>
       </c>
+      <c r="K57" t="s">
+        <v>15</v>
+      </c>
       <c r="L57" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="58" ht="42" spans="1:12">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="58" ht="55.5" spans="1:12">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B58" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
@@ -5096,7 +5093,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5108,57 +5105,57 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="L58" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="59" ht="55.5" spans="1:12">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s">
+        <v>72</v>
+      </c>
+      <c r="C59" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s">
+        <v>194</v>
+      </c>
+      <c r="H59" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" t="s">
+        <v>15</v>
+      </c>
+      <c r="L59" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="60" ht="27" spans="1:12">
+      <c r="A60" t="s">
+        <v>196</v>
+      </c>
+      <c r="B60" t="s">
         <v>13</v>
       </c>
-      <c r="C59" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" t="s">
-        <v>51</v>
-      </c>
-      <c r="E59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" t="s">
-        <v>15</v>
-      </c>
-      <c r="G59" t="s">
-        <v>193</v>
-      </c>
-      <c r="H59" t="s">
-        <v>15</v>
-      </c>
-      <c r="I59" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" t="s">
-        <v>15</v>
-      </c>
-      <c r="K59" t="s">
-        <v>57</v>
-      </c>
-      <c r="L59" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12">
-      <c r="A60" t="s">
-        <v>195</v>
-      </c>
-      <c r="B60" t="s">
-        <v>72</v>
-      </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
@@ -5172,7 +5169,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5187,53 +5184,53 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" ht="27" spans="1:12">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C61" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" t="s">
+        <v>51</v>
+      </c>
+      <c r="E61" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s">
+        <v>200</v>
+      </c>
+      <c r="H61" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" t="s">
+        <v>53</v>
+      </c>
+      <c r="L61" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="62" ht="54" spans="1:12">
+      <c r="A62" t="s">
+        <v>202</v>
+      </c>
+      <c r="B62" t="s">
         <v>13</v>
-      </c>
-      <c r="C61" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" t="s">
-        <v>199</v>
-      </c>
-      <c r="H61" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" t="s">
-        <v>15</v>
-      </c>
-      <c r="K61" t="s">
-        <v>15</v>
-      </c>
-      <c r="L61" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="62" ht="27" spans="1:12">
-      <c r="A62" t="s">
-        <v>201</v>
-      </c>
-      <c r="B62" t="s">
-        <v>50</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -5248,7 +5245,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5260,57 +5257,57 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L62" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="63" ht="54" spans="1:12">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="63" ht="40.5" spans="1:12">
       <c r="A63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B63" t="s">
+        <v>72</v>
+      </c>
+      <c r="C63" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s">
+        <v>206</v>
+      </c>
+      <c r="H63" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" t="s">
+        <v>15</v>
+      </c>
+      <c r="J63" t="s">
+        <v>15</v>
+      </c>
+      <c r="K63" t="s">
+        <v>15</v>
+      </c>
+      <c r="L63" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="64" ht="55.5" spans="1:12">
+      <c r="A64" t="s">
+        <v>208</v>
+      </c>
+      <c r="B64" t="s">
         <v>13</v>
       </c>
-      <c r="C63" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" t="s">
-        <v>51</v>
-      </c>
-      <c r="E63" t="s">
-        <v>15</v>
-      </c>
-      <c r="F63" t="s">
-        <v>15</v>
-      </c>
-      <c r="G63" t="s">
-        <v>205</v>
-      </c>
-      <c r="H63" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" t="s">
-        <v>15</v>
-      </c>
-      <c r="J63" t="s">
-        <v>15</v>
-      </c>
-      <c r="K63" t="s">
-        <v>57</v>
-      </c>
-      <c r="L63" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="64" ht="40.5" spans="1:12">
-      <c r="A64" t="s">
-        <v>207</v>
-      </c>
-      <c r="B64" t="s">
-        <v>72</v>
-      </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
@@ -5324,7 +5321,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5335,16 +5332,13 @@
       <c r="J64" t="s">
         <v>15</v>
       </c>
-      <c r="K64" t="s">
-        <v>15</v>
-      </c>
       <c r="L64" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="65" ht="55.5" spans="1:12">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65" ht="27" spans="1:12">
       <c r="A65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5362,7 +5356,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5373,13 +5367,16 @@
       <c r="J65" t="s">
         <v>15</v>
       </c>
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
       <c r="L65" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="66" ht="27" spans="1:12">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5397,7 +5394,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5412,12 +5409,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" ht="54" spans="1:12">
       <c r="A67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5435,7 +5432,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5447,15 +5444,15 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="L67" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="68" ht="54" spans="1:12">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="68" ht="27" spans="1:12">
       <c r="A68" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5473,7 +5470,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5485,15 +5482,15 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>221</v>
+        <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="69" ht="27" spans="1:12">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="69" ht="54" spans="1:12">
       <c r="A69" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5511,7 +5508,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5526,12 +5523,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="70" ht="54" spans="1:12">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="70" ht="40.5" spans="1:12">
       <c r="A70" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5549,7 +5546,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5564,54 +5561,54 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="71" ht="40.5" spans="1:12">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B71" t="s">
+        <v>50</v>
+      </c>
+      <c r="C71" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" t="s">
+        <v>231</v>
+      </c>
+      <c r="H71" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" t="s">
+        <v>15</v>
+      </c>
+      <c r="J71" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71" t="s">
+        <v>232</v>
+      </c>
+      <c r="L71" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="72" ht="54" spans="1:12">
+      <c r="A72" t="s">
+        <v>234</v>
+      </c>
+      <c r="B72" t="s">
         <v>13</v>
       </c>
-      <c r="C71" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" t="s">
-        <v>15</v>
-      </c>
-      <c r="E71" t="s">
-        <v>15</v>
-      </c>
-      <c r="F71" t="s">
-        <v>15</v>
-      </c>
-      <c r="G71" t="s">
-        <v>230</v>
-      </c>
-      <c r="H71" t="s">
-        <v>15</v>
-      </c>
-      <c r="I71" t="s">
-        <v>15</v>
-      </c>
-      <c r="J71" t="s">
-        <v>15</v>
-      </c>
-      <c r="K71" t="s">
-        <v>15</v>
-      </c>
-      <c r="L71" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" t="s">
-        <v>232</v>
-      </c>
-      <c r="B72" t="s">
-        <v>50</v>
-      </c>
       <c r="C72" t="s">
         <v>14</v>
       </c>
@@ -5625,27 +5622,27 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
       </c>
       <c r="I72" t="s">
-        <v>15</v>
+        <v>236</v>
       </c>
       <c r="J72" t="s">
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>234</v>
+        <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="73" ht="54" spans="1:12">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5663,13 +5660,13 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
       </c>
       <c r="I73" t="s">
-        <v>238</v>
+        <v>15</v>
       </c>
       <c r="J73" t="s">
         <v>15</v>
@@ -5678,12 +5675,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" ht="30" spans="1:12">
       <c r="A74" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5701,27 +5698,27 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
       </c>
       <c r="I74" t="s">
-        <v>15</v>
+        <v>243</v>
       </c>
       <c r="J74" t="s">
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="L74" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="75" ht="30" spans="1:12">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="75" ht="67.5" spans="1:12">
       <c r="A75" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5739,27 +5736,27 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
       </c>
       <c r="I75" t="s">
-        <v>245</v>
+        <v>15</v>
       </c>
       <c r="J75" t="s">
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>15</v>
+        <v>248</v>
       </c>
       <c r="L75" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="76" ht="67.5" spans="1:12">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="76" ht="54" spans="1:12">
       <c r="A76" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5777,7 +5774,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5789,56 +5786,56 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>249</v>
+        <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="77" ht="54" spans="1:12">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="77" ht="27" spans="1:12">
       <c r="A77" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
+        <v>50</v>
+      </c>
+      <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
+        <v>51</v>
+      </c>
+      <c r="E77" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
+        <v>254</v>
+      </c>
+      <c r="H77" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>53</v>
+      </c>
+      <c r="L77" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="78" ht="67.5" spans="1:12">
+      <c r="A78" t="s">
+        <v>256</v>
+      </c>
+      <c r="B78" t="s">
         <v>13</v>
-      </c>
-      <c r="C77" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" t="s">
-        <v>15</v>
-      </c>
-      <c r="E77" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" t="s">
-        <v>252</v>
-      </c>
-      <c r="H77" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" t="s">
-        <v>15</v>
-      </c>
-      <c r="J77" t="s">
-        <v>15</v>
-      </c>
-      <c r="K77" t="s">
-        <v>15</v>
-      </c>
-      <c r="L77" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="78" ht="27" spans="1:12">
-      <c r="A78" t="s">
-        <v>254</v>
-      </c>
-      <c r="B78" t="s">
-        <v>50</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -5853,7 +5850,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5865,15 +5862,15 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L78" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79" ht="67.5" spans="1:12">
       <c r="A79" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5882,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -5891,7 +5888,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5903,15 +5900,15 @@
         <v>15</v>
       </c>
       <c r="K79" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80" ht="67.5" spans="1:12">
       <c r="A80" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5929,7 +5926,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5944,54 +5941,54 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="81" ht="67.5" spans="1:12">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B81" t="s">
+        <v>72</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F81" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" t="s">
+        <v>266</v>
+      </c>
+      <c r="H81" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" t="s">
+        <v>15</v>
+      </c>
+      <c r="L81" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="82" ht="27" spans="1:12">
+      <c r="A82" t="s">
+        <v>268</v>
+      </c>
+      <c r="B82" t="s">
         <v>13</v>
       </c>
-      <c r="C81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" t="s">
-        <v>15</v>
-      </c>
-      <c r="E81" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G81" t="s">
-        <v>264</v>
-      </c>
-      <c r="H81" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K81" t="s">
-        <v>15</v>
-      </c>
-      <c r="L81" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12">
-      <c r="A82" t="s">
-        <v>266</v>
-      </c>
-      <c r="B82" t="s">
-        <v>72</v>
-      </c>
       <c r="C82" t="s">
         <v>14</v>
       </c>
@@ -6005,7 +6002,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -6020,53 +6017,53 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="83" ht="27" spans="1:12">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="83" ht="28.5" spans="1:12">
       <c r="A83" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B83" t="s">
+        <v>50</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>51</v>
+      </c>
+      <c r="E83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s">
+        <v>272</v>
+      </c>
+      <c r="H83" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" t="s">
+        <v>15</v>
+      </c>
+      <c r="K83" t="s">
+        <v>53</v>
+      </c>
+      <c r="L83" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="84" ht="40.5" spans="1:12">
+      <c r="A84" t="s">
+        <v>274</v>
+      </c>
+      <c r="B84" t="s">
         <v>13</v>
-      </c>
-      <c r="C83" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" t="s">
-        <v>15</v>
-      </c>
-      <c r="E83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" t="s">
-        <v>15</v>
-      </c>
-      <c r="G83" t="s">
-        <v>270</v>
-      </c>
-      <c r="H83" t="s">
-        <v>15</v>
-      </c>
-      <c r="I83" t="s">
-        <v>15</v>
-      </c>
-      <c r="J83" t="s">
-        <v>15</v>
-      </c>
-      <c r="K83" t="s">
-        <v>15</v>
-      </c>
-      <c r="L83" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="84" ht="28.5" spans="1:12">
-      <c r="A84" t="s">
-        <v>272</v>
-      </c>
-      <c r="B84" t="s">
-        <v>50</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -6081,7 +6078,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6092,16 +6089,16 @@
       <c r="J84" t="s">
         <v>15</v>
       </c>
-      <c r="K84" t="s">
-        <v>53</v>
+      <c r="K84" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="L84" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="85" ht="40.5" spans="1:12">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="85" ht="90" spans="1:12">
       <c r="A85" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6110,7 +6107,7 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E85" t="s">
         <v>15</v>
@@ -6119,7 +6116,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6130,16 +6127,13 @@
       <c r="J85" t="s">
         <v>15</v>
       </c>
-      <c r="K85" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="L85" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="86" ht="90" spans="1:12">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="86" ht="30" spans="1:12">
       <c r="A86" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6157,7 +6151,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6168,13 +6162,16 @@
       <c r="J86" t="s">
         <v>15</v>
       </c>
+      <c r="K86" t="s">
+        <v>15</v>
+      </c>
       <c r="L86" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="87" ht="30" spans="1:12">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6192,7 +6189,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6204,15 +6201,15 @@
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="L87" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="88" ht="40.5" spans="1:12">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6229,9 +6226,6 @@
       <c r="F88" t="s">
         <v>15</v>
       </c>
-      <c r="G88" t="s">
-        <v>286</v>
-      </c>
       <c r="H88" t="s">
         <v>15</v>
       </c>
@@ -6241,52 +6235,55 @@
       <c r="J88" t="s">
         <v>15</v>
       </c>
-      <c r="K88" t="s">
-        <v>287</v>
-      </c>
       <c r="L88" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="89" ht="30" spans="1:12">
       <c r="A89" t="s">
         <v>289</v>
       </c>
       <c r="B89" t="s">
+        <v>72</v>
+      </c>
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" t="s">
+        <v>290</v>
+      </c>
+      <c r="H89" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" t="s">
+        <v>15</v>
+      </c>
+      <c r="J89" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" t="s">
+        <v>137</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="90" ht="57" spans="1:12">
+      <c r="A90" t="s">
+        <v>292</v>
+      </c>
+      <c r="B90" t="s">
         <v>13</v>
       </c>
-      <c r="C89" t="s">
-        <v>14</v>
-      </c>
-      <c r="D89" t="s">
-        <v>15</v>
-      </c>
-      <c r="E89" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" t="s">
-        <v>15</v>
-      </c>
-      <c r="H89" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" t="s">
-        <v>15</v>
-      </c>
-      <c r="J89" t="s">
-        <v>15</v>
-      </c>
-      <c r="L89" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="90" ht="30" spans="1:12">
-      <c r="A90" t="s">
-        <v>290</v>
-      </c>
-      <c r="B90" t="s">
-        <v>72</v>
-      </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
@@ -6300,7 +6297,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6312,15 +6309,15 @@
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>137</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="91" ht="57" spans="1:12">
+        <v>15</v>
+      </c>
+      <c r="L90" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="91" ht="40.5" spans="1:12">
       <c r="A91" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6338,7 +6335,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6353,12 +6350,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="92" ht="40.5" spans="1:12">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" ht="27" spans="1:12">
       <c r="A92" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6376,7 +6373,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6391,12 +6388,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="93" ht="27" spans="1:12">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="93" ht="40.5" spans="1:12">
       <c r="A93" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6414,7 +6411,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6429,12 +6426,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="94" ht="40.5" spans="1:12">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="94" ht="54" spans="1:12">
       <c r="A94" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6452,7 +6449,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6463,49 +6460,11 @@
       <c r="J94" t="s">
         <v>15</v>
       </c>
-      <c r="K94" t="s">
-        <v>15</v>
+      <c r="K94" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="L94" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="95" ht="54" spans="1:12">
-      <c r="A95" t="s">
-        <v>303</v>
-      </c>
-      <c r="B95" t="s">
-        <v>13</v>
-      </c>
-      <c r="C95" t="s">
-        <v>14</v>
-      </c>
-      <c r="D95" t="s">
-        <v>15</v>
-      </c>
-      <c r="E95" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" t="s">
-        <v>15</v>
-      </c>
-      <c r="G95" t="s">
-        <v>304</v>
-      </c>
-      <c r="H95" t="s">
-        <v>15</v>
-      </c>
-      <c r="I95" t="s">
-        <v>15</v>
-      </c>
-      <c r="J95" t="s">
-        <v>15</v>
-      </c>
-      <c r="K95" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="L95" t="s">
-        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -6526,39 +6485,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2" t="s">
         <v>309</v>
-      </c>
-      <c r="B2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B3" t="s">
         <v>311</v>
-      </c>
-      <c r="B3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6566,7 +6525,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -6574,7 +6533,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6582,7 +6541,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
@@ -6590,7 +6549,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B9" t="s">
         <v>71</v>
@@ -6598,50 +6557,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
+        <v>318</v>
+      </c>
+      <c r="B10" t="s">
         <v>319</v>
-      </c>
-      <c r="B10" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -6663,616 +6622,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" t="s">
         <v>332</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>333</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>334</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>335</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>336</v>
-      </c>
-      <c r="F2" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C3" t="s">
         <v>338</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>339</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>340</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>341</v>
-      </c>
-      <c r="F3" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C4" t="s">
         <v>343</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>344</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>345</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>346</v>
-      </c>
-      <c r="F4" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C5" t="s">
         <v>348</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>349</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>350</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>351</v>
-      </c>
-      <c r="F5" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" t="s">
         <v>353</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>354</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>355</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>356</v>
-      </c>
-      <c r="F6" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C7" t="s">
         <v>358</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>359</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>360</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>361</v>
-      </c>
-      <c r="F7" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
+        <v>362</v>
+      </c>
+      <c r="B8" t="s">
         <v>363</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>364</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>365</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>366</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>367</v>
-      </c>
-      <c r="F8" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B9" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" t="s">
         <v>369</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>370</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>371</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>372</v>
-      </c>
-      <c r="F9" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
+        <v>373</v>
+      </c>
+      <c r="B10" t="s">
         <v>374</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>375</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>376</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>377</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>378</v>
-      </c>
-      <c r="F10" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B11" t="s">
+        <v>379</v>
+      </c>
+      <c r="C11" t="s">
         <v>380</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>381</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>382</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>383</v>
-      </c>
-      <c r="F11" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C12" t="s">
         <v>385</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>386</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>387</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>388</v>
-      </c>
-      <c r="F12" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B13" t="s">
+        <v>389</v>
+      </c>
+      <c r="C13" t="s">
         <v>390</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>391</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>392</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>393</v>
-      </c>
-      <c r="F13" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B14" t="s">
+        <v>394</v>
+      </c>
+      <c r="C14" t="s">
         <v>395</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>396</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>397</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>398</v>
-      </c>
-      <c r="F14" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B15" t="s">
+        <v>399</v>
+      </c>
+      <c r="C15" t="s">
         <v>400</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>401</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>402</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>403</v>
-      </c>
-      <c r="F15" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B16" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16" t="s">
         <v>405</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>406</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>407</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>408</v>
-      </c>
-      <c r="F16" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B17" t="s">
+        <v>409</v>
+      </c>
+      <c r="C17" t="s">
         <v>410</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>411</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>412</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>413</v>
-      </c>
-      <c r="F17" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B18" t="s">
+        <v>414</v>
+      </c>
+      <c r="C18" t="s">
         <v>415</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>416</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>417</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>418</v>
-      </c>
-      <c r="F18" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B19" t="s">
+        <v>419</v>
+      </c>
+      <c r="C19" t="s">
         <v>420</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>421</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>422</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>423</v>
-      </c>
-      <c r="F19" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B20" t="s">
+        <v>424</v>
+      </c>
+      <c r="C20" t="s">
         <v>425</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>426</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>427</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>428</v>
-      </c>
-      <c r="F20" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B21" t="s">
+        <v>429</v>
+      </c>
+      <c r="C21" t="s">
         <v>430</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>431</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>432</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>433</v>
-      </c>
-      <c r="F21" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B22" t="s">
+        <v>434</v>
+      </c>
+      <c r="C22" t="s">
         <v>435</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>436</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>437</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>438</v>
-      </c>
-      <c r="F22" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B23" t="s">
+        <v>439</v>
+      </c>
+      <c r="C23" t="s">
         <v>440</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>441</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>442</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>443</v>
-      </c>
-      <c r="F23" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B24" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" t="s">
         <v>445</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>386</v>
+      </c>
+      <c r="E24" t="s">
         <v>446</v>
       </c>
-      <c r="D24" t="s">
-        <v>387</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>447</v>
-      </c>
-      <c r="F24" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
+        <v>448</v>
+      </c>
+      <c r="B25" t="s">
         <v>449</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>450</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>451</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>452</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>453</v>
-      </c>
-      <c r="F25" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B26" t="s">
+        <v>454</v>
+      </c>
+      <c r="C26" t="s">
         <v>455</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>456</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>457</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>458</v>
-      </c>
-      <c r="F26" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B27" t="s">
+        <v>459</v>
+      </c>
+      <c r="C27" t="s">
         <v>460</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>461</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>462</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>463</v>
-      </c>
-      <c r="F27" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B28" t="s">
+        <v>464</v>
+      </c>
+      <c r="C28" t="s">
         <v>465</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>461</v>
+      </c>
+      <c r="E28" t="s">
         <v>466</v>
       </c>
-      <c r="D28" t="s">
-        <v>462</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>467</v>
-      </c>
-      <c r="F28" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B29" t="s">
+        <v>468</v>
+      </c>
+      <c r="C29" t="s">
         <v>469</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>470</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>471</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>472</v>
-      </c>
-      <c r="F29" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B30" t="s">
+        <v>473</v>
+      </c>
+      <c r="C30" t="s">
         <v>474</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>475</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>476</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>477</v>
-      </c>
-      <c r="F30" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
+        <v>478</v>
+      </c>
+      <c r="B31" t="s">
         <v>479</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>480</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>481</v>
-      </c>
-      <c r="D31" t="s">
-        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20385" windowHeight="10605"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线3层（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="482">
   <si>
     <t>ID</t>
   </si>
@@ -2985,9 +2985,7 @@
       <c r="J2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
+      <c r="K2"/>
       <c r="L2" t="s">
         <v>18</v>
       </c>
